--- a/experiments/results/densenet101/CIFAR-100/ReAct+DICE/adaptive/std/results.xlsx
+++ b/experiments/results/densenet101/CIFAR-100/ReAct+DICE/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -1107,6 +1107,55 @@
       <c r="O15" s="5" t="inlineStr">
         <is>
           <t>dice_p=90,ash_p=None,react_th=1.8,scale_th=0.01,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>96.59</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>88.94</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>70.53</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>92.52</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>92.38</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>99.42</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="M16" s="5" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="N16" s="5" t="n">
+        <v>90.56999999999999</v>
+      </c>
+      <c r="O16" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=90,ash_p=None,react_th=1.8,scale_th=0.5,type=std</t>
         </is>
       </c>
     </row>
